--- a/IFD04D.xlsx
+++ b/IFD04D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="359">
   <si>
     <t/>
   </si>
@@ -220,6 +220,18 @@
     <t>TASTY BAKMI YKNKU115</t>
   </si>
   <si>
+    <t>20032100</t>
+  </si>
+  <si>
+    <t>INDOMIE KRT/AYM PG90</t>
+  </si>
+  <si>
+    <t>20032099</t>
+  </si>
+  <si>
+    <t>INDOMIE KRT/GR.SPC90</t>
+  </si>
+  <si>
     <t>20143284</t>
   </si>
   <si>
@@ -460,25 +472,19 @@
     <t>INDOMIE GR AYM.GP 85</t>
   </si>
   <si>
-    <t>20032100</t>
-  </si>
-  <si>
-    <t>INDOMIE KRT/AYM PG90</t>
+    <t>10003800</t>
+  </si>
+  <si>
+    <t>INDOMI GR SP JUMB129</t>
   </si>
   <si>
     <t>14</t>
   </si>
   <si>
-    <t>20032099</t>
-  </si>
-  <si>
-    <t>INDOMIE KRT/GR.SPC90</t>
-  </si>
-  <si>
-    <t>10003800</t>
-  </si>
-  <si>
-    <t>INDOMI GR SP JUMB129</t>
+    <t>20130807</t>
+  </si>
+  <si>
+    <t>INDOMIE GRG RNDNG120</t>
   </si>
   <si>
     <t>10003801</t>
@@ -487,12 +493,6 @@
     <t>INDOMI JMB AYM PG127</t>
   </si>
   <si>
-    <t>20130807</t>
-  </si>
-  <si>
-    <t>INDOMIE GRG RNDNG120</t>
-  </si>
-  <si>
     <t>20142599</t>
   </si>
   <si>
@@ -541,22 +541,28 @@
     <t>BIHUN JAGUNG 320G</t>
   </si>
   <si>
+    <t>20138950</t>
+  </si>
+  <si>
+    <t>IDM ABON AYAM 80G</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
     <t>20003915</t>
   </si>
   <si>
     <t>IDM ABON SAPI 100GR</t>
   </si>
   <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20138950</t>
-  </si>
-  <si>
-    <t>IDM ABON AYAM 80G</t>
+    <t>20143959</t>
+  </si>
+  <si>
+    <t>IDM ABN SPI PDS 100G</t>
   </si>
   <si>
     <t>10000245</t>
@@ -595,6 +601,12 @@
     <t>MIGELAS SOTO AYAM 6S</t>
   </si>
   <si>
+    <t>20117989</t>
+  </si>
+  <si>
+    <t>M/S TOPOKKI ORI 132G</t>
+  </si>
+  <si>
     <t>20099679</t>
   </si>
   <si>
@@ -724,12 +736,6 @@
     <t>SMYANG QTR.CHSE 145G</t>
   </si>
   <si>
-    <t>20117989</t>
-  </si>
-  <si>
-    <t>M/S TOPOKKI ORI 132G</t>
-  </si>
-  <si>
     <t>20031775</t>
   </si>
   <si>
@@ -949,13 +955,13 @@
     <t>10014293</t>
   </si>
   <si>
-    <t>POP MIE SOTO AYM 75G</t>
+    <t>POP MIE SOTO AY 75 G</t>
   </si>
   <si>
     <t>20136587</t>
   </si>
   <si>
-    <t>POP MI INDOMIE GR 80</t>
+    <t>POP MIE INDM GR 80 G</t>
   </si>
   <si>
     <t>20140189</t>
@@ -1006,7 +1012,7 @@
     <t>10014292</t>
   </si>
   <si>
-    <t>POP MIE KRI AYM 75G</t>
+    <t>POP MIE KRI AYM 75 G</t>
   </si>
   <si>
     <t>28</t>
@@ -1015,19 +1021,34 @@
     <t>10000975</t>
   </si>
   <si>
-    <t>POP MIE AYAM 75G</t>
+    <t>POP MIE AYAM 75 G</t>
   </si>
   <si>
     <t>10000861</t>
   </si>
   <si>
-    <t>POP MIE BASO 75G</t>
+    <t>POP MIE BASO 75 G</t>
   </si>
   <si>
     <t>20087155</t>
   </si>
   <si>
-    <t>POP MIE AYM BWG 75G</t>
+    <t>POP MIE AYM BWG 75 G</t>
+  </si>
+  <si>
+    <t>20143961</t>
+  </si>
+  <si>
+    <t>P/MIE SPCY TORIMEN79</t>
+  </si>
+  <si>
+    <t>,(E-2B)</t>
+  </si>
+  <si>
+    <t>20143962</t>
+  </si>
+  <si>
+    <t>P/MIE CHICKEN YUZU75</t>
   </si>
   <si>
     <t>20055742</t>
@@ -1459,7 +1480,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F159"/>
+  <dimension ref="A1:F162"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2081,13 +2102,13 @@
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -2101,13 +2122,13 @@
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -2124,7 +2145,7 @@
         <v>15</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>19</v>
@@ -2144,7 +2165,7 @@
         <v>15</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>19</v>
@@ -2164,10 +2185,10 @@
         <v>15</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -2184,10 +2205,10 @@
         <v>15</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -2204,7 +2225,7 @@
         <v>15</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>6</v>
@@ -2224,7 +2245,7 @@
         <v>15</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>85</v>
+        <v>12</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>6</v>
@@ -2232,19 +2253,19 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B39" s="1" t="s">
-        <v>87</v>
-      </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>6</v>
@@ -2252,19 +2273,19 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="C40" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E40" s="1" t="s">
         <v>89</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>6</v>
@@ -2281,10 +2302,10 @@
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>6</v>
@@ -2301,10 +2322,10 @@
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>6</v>
@@ -2321,10 +2342,10 @@
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>6</v>
@@ -2332,19 +2353,19 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>98</v>
-      </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>6</v>
@@ -2352,19 +2373,19 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="C45" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D45" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C45" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>96</v>
-      </c>
       <c r="E45" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>6</v>
@@ -2381,10 +2402,10 @@
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>6</v>
@@ -2401,10 +2422,10 @@
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>6</v>
@@ -2421,10 +2442,10 @@
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>6</v>
@@ -2432,19 +2453,19 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B49" s="1" t="s">
-        <v>109</v>
-      </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>6</v>
@@ -2452,19 +2473,19 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="C50" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D50" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C50" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>107</v>
-      </c>
       <c r="E50" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>6</v>
@@ -2481,10 +2502,10 @@
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>6</v>
@@ -2501,10 +2522,10 @@
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>6</v>
@@ -2521,10 +2542,10 @@
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>6</v>
@@ -2532,19 +2553,19 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B54" s="1" t="s">
-        <v>120</v>
-      </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>6</v>
@@ -2552,19 +2573,19 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="C55" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D55" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C55" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>118</v>
-      </c>
       <c r="E55" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>6</v>
@@ -2581,10 +2602,10 @@
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>6</v>
@@ -2601,10 +2622,10 @@
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>6</v>
@@ -2621,10 +2642,10 @@
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>6</v>
@@ -2641,10 +2662,10 @@
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>6</v>
@@ -2652,19 +2673,19 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B60" s="1" t="s">
-        <v>133</v>
-      </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>6</v>
@@ -2672,16 +2693,16 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="C61" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D61" s="1" t="s">
         <v>135</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>136</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>4</v>
@@ -2692,16 +2713,16 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B62" s="1" t="s">
-        <v>138</v>
-      </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>18</v>
@@ -2712,19 +2733,19 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B63" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="C63" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D63" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C63" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>136</v>
-      </c>
       <c r="E63" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>6</v>
@@ -2741,10 +2762,10 @@
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>6</v>
@@ -2761,10 +2782,10 @@
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>6</v>
@@ -2781,10 +2802,10 @@
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>6</v>
@@ -2801,10 +2822,10 @@
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>6</v>
@@ -2821,10 +2842,10 @@
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>6</v>
@@ -2832,19 +2853,19 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B69" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B69" s="1" t="s">
-        <v>153</v>
-      </c>
       <c r="C69" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>6</v>
@@ -2852,19 +2873,19 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="C70" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D70" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="C70" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>151</v>
-      </c>
       <c r="E70" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>6</v>
@@ -2881,10 +2902,10 @@
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>6</v>
@@ -2901,10 +2922,10 @@
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>6</v>
@@ -2921,10 +2942,10 @@
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>6</v>
@@ -3107,7 +3128,7 @@
         <v>5</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>6</v>
+        <v>179</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -3127,7 +3148,7 @@
         <v>26</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -3147,47 +3168,47 @@
         <v>9</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>188</v>
+        <v>19</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B85" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="B85" s="1" t="s">
+      <c r="C85" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F85" s="1" t="s">
         <v>190</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F85" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B86" s="1" t="s">
+      <c r="C86" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D86" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="C86" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>191</v>
-      </c>
       <c r="E86" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -3201,13 +3222,13 @@
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -3221,10 +3242,10 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>19</v>
@@ -3241,10 +3262,10 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>19</v>
@@ -3252,19 +3273,19 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="B90" s="1" t="s">
-        <v>202</v>
-      </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>19</v>
@@ -3272,19 +3293,19 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B91" s="1" t="s">
+      <c r="C91" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D91" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="C91" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>200</v>
-      </c>
       <c r="E91" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>19</v>
@@ -3301,10 +3322,10 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>19</v>
@@ -3321,13 +3342,13 @@
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -3341,13 +3362,13 @@
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -3361,13 +3382,13 @@
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -3381,30 +3402,30 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="B97" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="B97" s="1" t="s">
-        <v>217</v>
-      </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>19</v>
@@ -3412,19 +3433,19 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B98" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="B98" s="1" t="s">
+      <c r="C98" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D98" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="C98" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>215</v>
-      </c>
       <c r="E98" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>19</v>
@@ -3441,10 +3462,10 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>19</v>
@@ -3461,10 +3482,10 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>19</v>
@@ -3481,10 +3502,10 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>19</v>
@@ -3492,19 +3513,19 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="B102" s="1" t="s">
-        <v>228</v>
-      </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>19</v>
@@ -3512,22 +3533,22 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="B103" s="1" t="s">
+      <c r="C103" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D103" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="C103" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>226</v>
-      </c>
       <c r="E103" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -3541,13 +3562,13 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -3561,13 +3582,13 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -3581,13 +3602,13 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -3601,10 +3622,10 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>19</v>
@@ -3621,10 +3642,10 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>19</v>
@@ -3632,19 +3653,19 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="B109" s="1" t="s">
+      <c r="C109" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D109" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="C109" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>241</v>
-      </c>
       <c r="E109" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>19</v>
@@ -3661,10 +3682,10 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>19</v>
@@ -3681,10 +3702,10 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>19</v>
@@ -3701,10 +3722,10 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>19</v>
@@ -3721,10 +3742,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>19</v>
@@ -3741,10 +3762,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>19</v>
@@ -3761,10 +3782,10 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>4</v>
+        <v>89</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>19</v>
@@ -3772,19 +3793,19 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B116" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="B116" s="1" t="s">
+      <c r="C116" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D116" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="C116" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>256</v>
-      </c>
       <c r="E116" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>19</v>
@@ -3801,10 +3822,10 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>19</v>
@@ -3821,10 +3842,10 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>19</v>
@@ -3841,13 +3862,13 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -3861,10 +3882,10 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>6</v>
@@ -3872,22 +3893,22 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="B121" s="1" t="s">
+      <c r="C121" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D121" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="C121" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>267</v>
-      </c>
       <c r="E121" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>167</v>
+        <v>6</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
@@ -3901,10 +3922,10 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>167</v>
@@ -3921,13 +3942,13 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>6</v>
+        <v>167</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -3941,13 +3962,13 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -3961,10 +3982,10 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>19</v>
@@ -3972,19 +3993,19 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B126" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="B126" s="1" t="s">
+      <c r="C126" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D126" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="C126" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D126" s="1" t="s">
-        <v>278</v>
-      </c>
       <c r="E126" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>19</v>
@@ -4001,10 +4022,10 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>19</v>
@@ -4021,10 +4042,10 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>19</v>
@@ -4041,10 +4062,10 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>19</v>
@@ -4061,10 +4082,10 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>19</v>
@@ -4081,13 +4102,13 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>167</v>
+        <v>19</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -4101,10 +4122,10 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>167</v>
@@ -4121,10 +4142,10 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>167</v>
@@ -4141,30 +4162,30 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>297</v>
+        <v>280</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>19</v>
+        <v>167</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B135" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="B135" s="1" t="s">
+      <c r="C135" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D135" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="C135" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>297</v>
-      </c>
       <c r="E135" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>19</v>
@@ -4181,10 +4202,10 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>19</v>
@@ -4201,10 +4222,10 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>19</v>
@@ -4221,30 +4242,30 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B139" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="B139" s="1" t="s">
+      <c r="C139" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D139" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="C139" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>306</v>
-      </c>
       <c r="E139" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>6</v>
@@ -4261,10 +4282,10 @@
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>6</v>
@@ -4281,10 +4302,10 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>6</v>
@@ -4301,10 +4322,10 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>6</v>
@@ -4321,10 +4342,10 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>6</v>
@@ -4341,10 +4362,10 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>6</v>
@@ -4361,10 +4382,10 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>321</v>
+        <v>308</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>4</v>
+        <v>89</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>6</v>
@@ -4372,19 +4393,19 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B146" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="B146" s="1" t="s">
+      <c r="C146" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D146" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="C146" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D146" s="1" t="s">
-        <v>321</v>
-      </c>
       <c r="E146" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>6</v>
@@ -4401,10 +4422,10 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>6</v>
@@ -4421,10 +4442,10 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>6</v>
@@ -4441,10 +4462,10 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>6</v>
@@ -4461,10 +4482,10 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>6</v>
@@ -4472,19 +4493,19 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B151" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="B151" s="1" t="s">
+      <c r="C151" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D151" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="C151" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D151" s="1" t="s">
-        <v>332</v>
-      </c>
       <c r="E151" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>6</v>
@@ -4501,10 +4522,10 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>6</v>
@@ -4521,10 +4542,10 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>6</v>
@@ -4541,33 +4562,33 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B155" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="B155" s="1" t="s">
+      <c r="C155" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F155" s="1" t="s">
         <v>343</v>
-      </c>
-      <c r="C155" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D155" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="E155" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F155" s="1" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -4581,13 +4602,13 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>179</v>
+        <v>343</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -4601,52 +4622,112 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>179</v>
+        <v>19</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D158" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="B158" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="C158" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D158" s="1" t="s">
-        <v>341</v>
-      </c>
       <c r="E158" s="1" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>19</v>
+        <v>179</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="E159" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F159" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A160" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="E160" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F160" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A161" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="E161" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F161" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A162" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="E162" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F159" s="1" t="s">
+      <c r="F162" s="1" t="s">
         <v>19</v>
       </c>
     </row>

--- a/IFD04D.xlsx
+++ b/IFD04D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="358">
   <si>
     <t/>
   </si>
@@ -133,7 +133,7 @@
     <t>10023790</t>
   </si>
   <si>
-    <t>SEDAAP MIE AYM BWG70</t>
+    <t>SEDAAP MIE A/BW 70 G</t>
   </si>
   <si>
     <t>10023792</t>
@@ -145,19 +145,19 @@
     <t>10023791</t>
   </si>
   <si>
-    <t>SEDAAP MIE KR.AYAM72</t>
+    <t>SEDAAP MIE KR/A 72 G</t>
   </si>
   <si>
     <t>20131690</t>
   </si>
   <si>
-    <t>SEDAAP MIE AYM JRT77</t>
+    <t>SEDAAP MIE AYM 77 G</t>
   </si>
   <si>
     <t>20025418</t>
   </si>
   <si>
-    <t>SEDAAP MIE KARI SP75</t>
+    <t>SEDAAP MIE KR/S 75 G</t>
   </si>
   <si>
     <t>20049556</t>
@@ -181,7 +181,7 @@
     <t>20114755</t>
   </si>
   <si>
-    <t>SDP MIE SPC.LAKSA 83</t>
+    <t>SEDAAP MI S/LKS 83 G</t>
   </si>
   <si>
     <t>20125555</t>
@@ -235,25 +235,25 @@
     <t>20143284</t>
   </si>
   <si>
-    <t>WOWSPAGETIGORENG79G</t>
+    <t>WOW SPAGETI GRG 79 G</t>
   </si>
   <si>
     <t>20135312</t>
   </si>
   <si>
-    <t>WOW SPAGHETI CARB80</t>
+    <t>WOW SPAGETI CB 80 G</t>
   </si>
   <si>
     <t>20135313</t>
   </si>
   <si>
-    <t>WOW SPAGHETI BOLOG76</t>
+    <t>WOW SPAGETI BG 76 G</t>
   </si>
   <si>
     <t>20137860</t>
   </si>
   <si>
-    <t>WOW AGLI OLIO 75G</t>
+    <t>WOW SPAGETI AO 75 G</t>
   </si>
   <si>
     <t>20138738</t>
@@ -343,7 +343,7 @@
     <t>10000185</t>
   </si>
   <si>
-    <t>INDOMI KARI AYAM 72G</t>
+    <t>INDOMI KRI AYAM 72 G</t>
   </si>
   <si>
     <t>10</t>
@@ -376,7 +376,7 @@
     <t>20085115</t>
   </si>
   <si>
-    <t>INDOMI GRNG ACEH 90G</t>
+    <t>INDOMI GRNG ACH 90 G</t>
   </si>
   <si>
     <t>11</t>
@@ -391,7 +391,7 @@
     <t>20044199</t>
   </si>
   <si>
-    <t>INDOMIE GRG CB.IJO85</t>
+    <t>INDOMI GR C.IJO 85 G</t>
   </si>
   <si>
     <t>20138358</t>
@@ -415,7 +415,7 @@
     <t>10003517</t>
   </si>
   <si>
-    <t>INDOMI GORENG SPC 80</t>
+    <t>INDOMI GRNG SPC 80 G</t>
   </si>
   <si>
     <t>12</t>
@@ -424,7 +424,7 @@
     <t>20019930</t>
   </si>
   <si>
-    <t>INDOMIE GRG RNDANG91</t>
+    <t>INDOMI GR RNDNG 91 G</t>
   </si>
   <si>
     <t>20128381</t>
@@ -469,7 +469,7 @@
     <t>20093221</t>
   </si>
   <si>
-    <t>INDOMIE GR AYM.GP 85</t>
+    <t>INDOMI GR AY.GP 85 G</t>
   </si>
   <si>
     <t>10003800</t>
@@ -538,7 +538,7 @@
     <t>20034699</t>
   </si>
   <si>
-    <t>BIHUN JAGUNG 320G</t>
+    <t>C/TNM JGG BHN JGG320</t>
   </si>
   <si>
     <t>20138950</t>
@@ -1040,9 +1040,6 @@
   </si>
   <si>
     <t>P/MIE SPCY TORIMEN79</t>
-  </si>
-  <si>
-    <t>,(E-2B)</t>
   </si>
   <si>
     <t>20143962</t>
@@ -4588,15 +4585,15 @@
         <v>9</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>343</v>
+        <v>6</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="B156" s="1" t="s">
         <v>344</v>
-      </c>
-      <c r="B156" s="1" t="s">
-        <v>345</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>3</v>
@@ -4608,21 +4605,21 @@
         <v>12</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>343</v>
+        <v>6</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B157" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="B157" s="1" t="s">
+      <c r="C157" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D157" s="1" t="s">
         <v>347</v>
-      </c>
-      <c r="C157" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D157" s="1" t="s">
-        <v>348</v>
       </c>
       <c r="E157" s="1" t="s">
         <v>4</v>
@@ -4633,16 +4630,16 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="B158" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="B158" s="1" t="s">
-        <v>350</v>
-      </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E158" s="1" t="s">
         <v>18</v>
@@ -4653,16 +4650,16 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="B159" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="B159" s="1" t="s">
-        <v>352</v>
-      </c>
       <c r="C159" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E159" s="1" t="s">
         <v>5</v>
@@ -4673,16 +4670,16 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="B160" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="B160" s="1" t="s">
-        <v>354</v>
-      </c>
       <c r="C160" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E160" s="1" t="s">
         <v>26</v>
@@ -4693,16 +4690,16 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B161" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="B161" s="1" t="s">
-        <v>356</v>
-      </c>
       <c r="C161" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E161" s="1" t="s">
         <v>9</v>
@@ -4713,16 +4710,16 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="B162" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="B162" s="1" t="s">
-        <v>358</v>
-      </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E162" s="1" t="s">
         <v>12</v>

--- a/IFD04D.xlsx
+++ b/IFD04D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="972" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="978" uniqueCount="360">
   <si>
     <t/>
   </si>
@@ -100,124 +100,376 @@
     <t>SUKSES ISI2 ACEH 140</t>
   </si>
   <si>
+    <t>20131022</t>
+  </si>
+  <si>
+    <t>SDAAP MIE GRG BKED87</t>
+  </si>
+  <si>
+    <t>20132986</t>
+  </si>
+  <si>
+    <t>TASTY BAKMI TRYKI120</t>
+  </si>
+  <si>
+    <t>20094693</t>
+  </si>
+  <si>
+    <t>TASTY BAKMI AYM 5.5K</t>
+  </si>
+  <si>
+    <t>20119164</t>
+  </si>
+  <si>
+    <t>TASTY BAKMI YKNKU115</t>
+  </si>
+  <si>
+    <t>10023791</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE KR/A 72 G</t>
+  </si>
+  <si>
+    <t>20123024</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE STO.MDR82</t>
+  </si>
+  <si>
+    <t>20114755</t>
+  </si>
+  <si>
+    <t>SEDAAP MI S/LKS 83 G</t>
+  </si>
+  <si>
+    <t>10023790</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE A/BW 70 G</t>
+  </si>
+  <si>
+    <t>10023792</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE SOTO 76GR</t>
+  </si>
+  <si>
+    <t>20131690</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE AYM 77 G</t>
+  </si>
+  <si>
+    <t>20025418</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE KR/S 75 G</t>
+  </si>
+  <si>
+    <t>20136385</t>
+  </si>
+  <si>
+    <t>SEDAAP GRG CHF.DVN93</t>
+  </si>
+  <si>
+    <t>20096781</t>
+  </si>
+  <si>
+    <t>SEDAAP MI KR.SPCY 87</t>
+  </si>
+  <si>
+    <t>20125555</t>
+  </si>
+  <si>
+    <t>SEDAP MI KRN CH/BL86</t>
+  </si>
+  <si>
+    <t>20049556</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE AYM KR 88</t>
+  </si>
+  <si>
+    <t>10023789</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE GORENG 91</t>
+  </si>
+  <si>
+    <t>20096589</t>
+  </si>
+  <si>
+    <t>SEDAAP MI GRG 5X91 G</t>
+  </si>
+  <si>
+    <t>20096590</t>
+  </si>
+  <si>
+    <t>SEDAAP MI STO 5x76 G</t>
+  </si>
+  <si>
+    <t>20140674</t>
+  </si>
+  <si>
+    <t>SEDAAP MI AYB 5x71 G</t>
+  </si>
+  <si>
+    <t>20143284</t>
+  </si>
+  <si>
+    <t>WOW SPAGETI GRG 79 G</t>
+  </si>
+  <si>
+    <t>20135312</t>
+  </si>
+  <si>
+    <t>WOW SPAGETI CB 80 G</t>
+  </si>
+  <si>
+    <t>20135313</t>
+  </si>
+  <si>
+    <t>WOW SPAGETI BG 76 G</t>
+  </si>
+  <si>
+    <t>20137860</t>
+  </si>
+  <si>
+    <t>WOW SPAGETI AO 75 G</t>
+  </si>
+  <si>
+    <t>20138738</t>
+  </si>
+  <si>
+    <t>I/POP SPGTI CRBO 80G</t>
+  </si>
+  <si>
+    <t>20138739</t>
+  </si>
+  <si>
+    <t>I/POP SPGTI BGLN 84G</t>
+  </si>
+  <si>
+    <t>20143393</t>
+  </si>
+  <si>
+    <t>I/P SPGT FR CKN CB80</t>
+  </si>
+  <si>
+    <t>20143392</t>
+  </si>
+  <si>
+    <t>I/POP SPGTI PZA BL80</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>20141466</t>
+  </si>
+  <si>
+    <t>RMN YES TKYO CHKN84G</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>20141464</t>
+  </si>
+  <si>
+    <t>RMN YES HKTA CHKN88G</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
     <t>10007606</t>
   </si>
   <si>
     <t>ABC MIE GULAI PDS.70</t>
   </si>
   <si>
-    <t>20131022</t>
-  </si>
-  <si>
-    <t>SDAAP MIE GRG BKED87</t>
-  </si>
-  <si>
-    <t>20096589</t>
-  </si>
-  <si>
-    <t>SEDAAP MI GRG 5X91 G</t>
-  </si>
-  <si>
-    <t>20096590</t>
-  </si>
-  <si>
-    <t>SEDAAP MI STO 5x76 G</t>
-  </si>
-  <si>
-    <t>20140674</t>
-  </si>
-  <si>
-    <t>SEDAAP MI AYB 5x71 G</t>
-  </si>
-  <si>
-    <t>10023790</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE A/BW 70 G</t>
-  </si>
-  <si>
-    <t>10023792</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE SOTO 76GR</t>
-  </si>
-  <si>
-    <t>10023791</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE KR/A 72 G</t>
-  </si>
-  <si>
-    <t>20131690</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE AYM 77 G</t>
-  </si>
-  <si>
-    <t>20025418</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE KR/S 75 G</t>
-  </si>
-  <si>
-    <t>20049556</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE AYM KR 88</t>
-  </si>
-  <si>
-    <t>20136385</t>
-  </si>
-  <si>
-    <t>SEDAAP GRG CHF.DVN93</t>
-  </si>
-  <si>
-    <t>20096781</t>
-  </si>
-  <si>
-    <t>SEDAAP MI KR.SPCY 87</t>
-  </si>
-  <si>
-    <t>20114755</t>
-  </si>
-  <si>
-    <t>SEDAAP MI S/LKS 83 G</t>
-  </si>
-  <si>
-    <t>20125555</t>
-  </si>
-  <si>
-    <t>SEDAP MI KRN CH/BL86</t>
-  </si>
-  <si>
-    <t>10023789</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE GORENG 91</t>
-  </si>
-  <si>
-    <t>20123024</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE STO.MDR82</t>
-  </si>
-  <si>
-    <t>20132986</t>
-  </si>
-  <si>
-    <t>TASTY BAKMI TRYKI120</t>
-  </si>
-  <si>
-    <t>20094693</t>
-  </si>
-  <si>
-    <t>TASTY BAKMI AYM 5.5K</t>
-  </si>
-  <si>
-    <t>20119164</t>
-  </si>
-  <si>
-    <t>TASTY BAKMI YKNKU115</t>
+    <t>10015954</t>
+  </si>
+  <si>
+    <t>GAGA 100 JALAPENO 75</t>
+  </si>
+  <si>
+    <t>20085444</t>
+  </si>
+  <si>
+    <t>GAGA 100 GR.JLPNO 85</t>
+  </si>
+  <si>
+    <t>10003435</t>
+  </si>
+  <si>
+    <t>SUPERMI AYAM BWG 75G</t>
+  </si>
+  <si>
+    <t>10000184</t>
+  </si>
+  <si>
+    <t>INDOMI AYAM SPECL68G</t>
+  </si>
+  <si>
+    <t>10000713</t>
+  </si>
+  <si>
+    <t>INDOMI KLD AYAM 75G</t>
+  </si>
+  <si>
+    <t>10002560</t>
+  </si>
+  <si>
+    <t>INDOMI SOTO MIE 70GR</t>
+  </si>
+  <si>
+    <t>20007834</t>
+  </si>
+  <si>
+    <t>INDOMIE SOTO SPCL 75</t>
+  </si>
+  <si>
+    <t>20085462</t>
+  </si>
+  <si>
+    <t>INDOMIE SOTO LMNG 80</t>
+  </si>
+  <si>
+    <t>20137101</t>
+  </si>
+  <si>
+    <t>INDOMIE SOTO PD.D 76</t>
+  </si>
+  <si>
+    <t>20137102</t>
+  </si>
+  <si>
+    <t>INDOMIE SOTO KN 76G</t>
+  </si>
+  <si>
+    <t>10000185</t>
+  </si>
+  <si>
+    <t>INDOMI KRI AYAM 72 G</t>
+  </si>
+  <si>
+    <t>10000652</t>
+  </si>
+  <si>
+    <t>INDOMI AYAM BWNG 69G</t>
+  </si>
+  <si>
+    <t>10035954</t>
+  </si>
+  <si>
+    <t>INDOMIE EMPL/GTNG 75</t>
+  </si>
+  <si>
+    <t>10035955</t>
+  </si>
+  <si>
+    <t>INDOMIE MI KOCOK 75G</t>
+  </si>
+  <si>
+    <t>20085115</t>
+  </si>
+  <si>
+    <t>INDOMI GRNG ACH 90 G</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>20074112</t>
+  </si>
+  <si>
+    <t>INDOMIE GRG RICA 85G</t>
+  </si>
+  <si>
+    <t>20044199</t>
+  </si>
+  <si>
+    <t>INDOMI GR C.IJO 85 G</t>
+  </si>
+  <si>
+    <t>20138358</t>
+  </si>
+  <si>
+    <t>INDOMI NYEMK B/LDS80</t>
+  </si>
+  <si>
+    <t>20140632</t>
+  </si>
+  <si>
+    <t>INDOMI NYMEK J/RD 84</t>
+  </si>
+  <si>
+    <t>20133372</t>
+  </si>
+  <si>
+    <t>INDOMIE RWN MERCON75</t>
+  </si>
+  <si>
+    <t>10003517</t>
+  </si>
+  <si>
+    <t>INDOMI GRNG SPC 80 G</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>20019930</t>
+  </si>
+  <si>
+    <t>INDOMI GR RNDNG 91 G</t>
+  </si>
+  <si>
+    <t>20128381</t>
+  </si>
+  <si>
+    <t>INDOMI TRI MSO RMN86</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>20132338</t>
+  </si>
+  <si>
+    <t>INDOMIE TORI KARA 89</t>
+  </si>
+  <si>
+    <t>20135989</t>
+  </si>
+  <si>
+    <t>INDOMI SPCY RMYEON83</t>
+  </si>
+  <si>
+    <t>20135990</t>
+  </si>
+  <si>
+    <t>INDOMI FIERY CHKIN94</t>
+  </si>
+  <si>
+    <t>20136533</t>
+  </si>
+  <si>
+    <t>INDOMIE K-ROSE 85G</t>
+  </si>
+  <si>
+    <t>20101747</t>
+  </si>
+  <si>
+    <t>INDOMI SBLAK HOT/J75</t>
+  </si>
+  <si>
+    <t>20093221</t>
+  </si>
+  <si>
+    <t>INDOMI GR AY.GP 85 G</t>
   </si>
   <si>
     <t>20032100</t>
@@ -226,277 +478,37 @@
     <t>INDOMIE KRT/AYM PG90</t>
   </si>
   <si>
+    <t>14</t>
+  </si>
+  <si>
     <t>20032099</t>
   </si>
   <si>
     <t>INDOMIE KRT/GR.SPC90</t>
   </si>
   <si>
-    <t>20143284</t>
-  </si>
-  <si>
-    <t>WOW SPAGETI GRG 79 G</t>
-  </si>
-  <si>
-    <t>20135312</t>
-  </si>
-  <si>
-    <t>WOW SPAGETI CB 80 G</t>
-  </si>
-  <si>
-    <t>20135313</t>
-  </si>
-  <si>
-    <t>WOW SPAGETI BG 76 G</t>
-  </si>
-  <si>
-    <t>20137860</t>
-  </si>
-  <si>
-    <t>WOW SPAGETI AO 75 G</t>
-  </si>
-  <si>
-    <t>20138738</t>
-  </si>
-  <si>
-    <t>I/POP SPGTI CRBO 80G</t>
-  </si>
-  <si>
-    <t>20138739</t>
-  </si>
-  <si>
-    <t>I/POP SPGTI BGLN 84G</t>
-  </si>
-  <si>
-    <t>20143393</t>
-  </si>
-  <si>
-    <t>I/P SPGT FR CKN CB80</t>
-  </si>
-  <si>
-    <t>20143392</t>
-  </si>
-  <si>
-    <t>I/POP SPGTI PZA BL80</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>10003435</t>
-  </si>
-  <si>
-    <t>SUPERMI AYAM BWG 75G</t>
-  </si>
-  <si>
-    <t>10015954</t>
-  </si>
-  <si>
-    <t>GAGA 100 JALAPENO 75</t>
-  </si>
-  <si>
-    <t>20085444</t>
-  </si>
-  <si>
-    <t>GAGA 100 GR.JLPNO 85</t>
-  </si>
-  <si>
-    <t>10000713</t>
-  </si>
-  <si>
-    <t>INDOMI KLD AYAM 75G</t>
-  </si>
-  <si>
-    <t>10002560</t>
-  </si>
-  <si>
-    <t>INDOMI SOTO MIE 70GR</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>20007834</t>
-  </si>
-  <si>
-    <t>INDOMIE SOTO SPCL 75</t>
-  </si>
-  <si>
-    <t>20085462</t>
-  </si>
-  <si>
-    <t>INDOMIE SOTO LMNG 80</t>
-  </si>
-  <si>
-    <t>20137101</t>
-  </si>
-  <si>
-    <t>INDOMIE SOTO PD.D 76</t>
-  </si>
-  <si>
-    <t>20137102</t>
-  </si>
-  <si>
-    <t>INDOMIE SOTO KN 76G</t>
-  </si>
-  <si>
-    <t>10000185</t>
-  </si>
-  <si>
-    <t>INDOMI KRI AYAM 72 G</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>10000652</t>
-  </si>
-  <si>
-    <t>INDOMI AYAM BWNG 69G</t>
-  </si>
-  <si>
-    <t>10000184</t>
-  </si>
-  <si>
-    <t>INDOMI AYAM SPECL68G</t>
-  </si>
-  <si>
-    <t>10035954</t>
-  </si>
-  <si>
-    <t>INDOMIE EMPL/GTNG 75</t>
-  </si>
-  <si>
-    <t>10035955</t>
-  </si>
-  <si>
-    <t>INDOMIE MI KOCOK 75G</t>
-  </si>
-  <si>
-    <t>20085115</t>
-  </si>
-  <si>
-    <t>INDOMI GRNG ACH 90 G</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>20074112</t>
-  </si>
-  <si>
-    <t>INDOMIE GRG RICA 85G</t>
-  </si>
-  <si>
-    <t>20044199</t>
-  </si>
-  <si>
-    <t>INDOMI GR C.IJO 85 G</t>
-  </si>
-  <si>
-    <t>20138358</t>
-  </si>
-  <si>
-    <t>INDOMI NYEMK B/LDS80</t>
-  </si>
-  <si>
-    <t>20140632</t>
-  </si>
-  <si>
-    <t>INDOMI NYMEK J/RD 84</t>
-  </si>
-  <si>
-    <t>20133372</t>
-  </si>
-  <si>
-    <t>INDOMIE RWN MERCON75</t>
-  </si>
-  <si>
-    <t>10003517</t>
-  </si>
-  <si>
-    <t>INDOMI GRNG SPC 80 G</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>20019930</t>
-  </si>
-  <si>
-    <t>INDOMI GR RNDNG 91 G</t>
-  </si>
-  <si>
-    <t>20128381</t>
-  </si>
-  <si>
-    <t>INDOMI TRI MSO RMN86</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>20132338</t>
-  </si>
-  <si>
-    <t>INDOMIE TORI KARA 89</t>
-  </si>
-  <si>
-    <t>20135989</t>
-  </si>
-  <si>
-    <t>INDOMI SPCY RMYEON83</t>
-  </si>
-  <si>
-    <t>20135990</t>
-  </si>
-  <si>
-    <t>INDOMI FIERY CHKIN94</t>
-  </si>
-  <si>
-    <t>20136533</t>
-  </si>
-  <si>
-    <t>INDOMIE K-ROSE 85G</t>
-  </si>
-  <si>
-    <t>20101747</t>
-  </si>
-  <si>
-    <t>INDOMI SBLAK HOT/J75</t>
-  </si>
-  <si>
-    <t>20093221</t>
-  </si>
-  <si>
-    <t>INDOMI GR AY.GP 85 G</t>
-  </si>
-  <si>
     <t>10003800</t>
   </si>
   <si>
-    <t>INDOMI GR SP JUMB129</t>
-  </si>
-  <si>
-    <t>14</t>
+    <t>INDOMI GR S.JB 129 G</t>
   </si>
   <si>
     <t>20130807</t>
   </si>
   <si>
-    <t>INDOMIE GRG RNDNG120</t>
+    <t>INDOMI GR RDNG 120 G</t>
   </si>
   <si>
     <t>10003801</t>
   </si>
   <si>
-    <t>INDOMI JMB AYM PG127</t>
+    <t>INDOMI JB A.PG 127 G</t>
   </si>
   <si>
     <t>20142599</t>
   </si>
   <si>
-    <t>INDOMI GR CB.IJO 120</t>
+    <t>INDOMI G C.IJO 120 G</t>
   </si>
   <si>
     <t>20085013</t>
@@ -535,6 +547,12 @@
     <t>AAA BIHUN 220GR</t>
   </si>
   <si>
+    <t>20140351</t>
+  </si>
+  <si>
+    <t>LARISST BHN JGG 200G</t>
+  </si>
+  <si>
     <t>20034699</t>
   </si>
   <si>
@@ -601,69 +619,69 @@
     <t>MIGELAS SOTO AYAM 6S</t>
   </si>
   <si>
+    <t>20099679</t>
+  </si>
+  <si>
+    <t>LEMONILO MIE GRG 65G</t>
+  </si>
+  <si>
+    <t>20113972</t>
+  </si>
+  <si>
+    <t>LEMONILO PDS KOREA68</t>
+  </si>
+  <si>
+    <t>20128247</t>
+  </si>
+  <si>
+    <t>WNHAE FRIED ROSE 97G</t>
+  </si>
+  <si>
+    <t>20141198</t>
+  </si>
+  <si>
+    <t>WONHAE TPOKI CARB 80</t>
+  </si>
+  <si>
+    <t>20127764</t>
+  </si>
+  <si>
+    <t>N/SHIM STR FRY 131 G</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>20138271</t>
+  </si>
+  <si>
+    <t>N/SHIM STR CHESE 136</t>
+  </si>
+  <si>
+    <t>20138170</t>
+  </si>
+  <si>
+    <t>N/SHIM SPCY CHK 120G</t>
+  </si>
+  <si>
+    <t>20141816</t>
+  </si>
+  <si>
+    <t>N/SHIM TOOMBA 137GR</t>
+  </si>
+  <si>
+    <t>20141070</t>
+  </si>
+  <si>
+    <t>KOBE MI CH/OIL LV.15</t>
+  </si>
+  <si>
     <t>20117989</t>
   </si>
   <si>
     <t>M/S TOPOKKI ORI 132G</t>
   </si>
   <si>
-    <t>20099679</t>
-  </si>
-  <si>
-    <t>LEMONILO MIE GRG 65G</t>
-  </si>
-  <si>
-    <t>20113972</t>
-  </si>
-  <si>
-    <t>LEMONILO PDS KOREA68</t>
-  </si>
-  <si>
-    <t>20127764</t>
-  </si>
-  <si>
-    <t>N/SHIM STR FRY 131 G</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>20138271</t>
-  </si>
-  <si>
-    <t>N/SHIM STR CHESE 136</t>
-  </si>
-  <si>
-    <t>20138170</t>
-  </si>
-  <si>
-    <t>N/SHIM SPCY CHK 120G</t>
-  </si>
-  <si>
-    <t>20141816</t>
-  </si>
-  <si>
-    <t>N/SHIM TOOMBA 137GR</t>
-  </si>
-  <si>
-    <t>20141070</t>
-  </si>
-  <si>
-    <t>KOBE MI CH/OIL LV.15</t>
-  </si>
-  <si>
-    <t>20128247</t>
-  </si>
-  <si>
-    <t>WNHAE FRIED ROSE 97G</t>
-  </si>
-  <si>
-    <t>20141198</t>
-  </si>
-  <si>
-    <t>WONHAE TPOKI CARB 80</t>
-  </si>
-  <si>
     <t>20135130</t>
   </si>
   <si>
@@ -757,18 +775,6 @@
     <t>NISSIN HOT CARBO 120</t>
   </si>
   <si>
-    <t>20141466</t>
-  </si>
-  <si>
-    <t>RMN YES TKYO CHKN84G</t>
-  </si>
-  <si>
-    <t>20141464</t>
-  </si>
-  <si>
-    <t>RMN YES HKTA CHKN88G</t>
-  </si>
-  <si>
     <t>20143800</t>
   </si>
   <si>
@@ -784,7 +790,7 @@
     <t>20039494</t>
   </si>
   <si>
-    <t>BIHUNKU AYM BWG 55G</t>
+    <t>BIHUNKU AYM BWG 55 G</t>
   </si>
   <si>
     <t>22</t>
@@ -793,19 +799,19 @@
     <t>10035852</t>
   </si>
   <si>
-    <t>BIHUNKU GRG SPCL 60G</t>
+    <t>BIHUNKU GR SPCL 60 G</t>
   </si>
   <si>
     <t>20069768</t>
   </si>
   <si>
-    <t>BIHUNKU SOTO SPS 55G</t>
+    <t>BIHUNKU STO SPS 55 G</t>
   </si>
   <si>
     <t>20141374</t>
   </si>
   <si>
-    <t>BIHUNKU BASO SAPI 50</t>
+    <t>BIHUNKU BSO SPI 50 G</t>
   </si>
   <si>
     <t>10000653</t>
@@ -1477,14 +1483,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F162"/>
+  <dimension ref="A1:F163"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="4" customWidth="1"/>
-    <col min="5" max="5" width="3" customWidth="1"/>
+    <col min="4" max="5" width="4" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1799,10 +1804,10 @@
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>19</v>
@@ -1822,7 +1827,7 @@
         <v>26</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>19</v>
@@ -1842,7 +1847,7 @@
         <v>26</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>19</v>
@@ -1862,7 +1867,7 @@
         <v>26</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>19</v>
@@ -1882,7 +1887,7 @@
         <v>26</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>19</v>
@@ -1902,7 +1907,7 @@
         <v>26</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>19</v>
@@ -1922,7 +1927,7 @@
         <v>26</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>19</v>
@@ -2019,10 +2024,10 @@
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>19</v>
@@ -2042,7 +2047,7 @@
         <v>12</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>19</v>
@@ -2062,7 +2067,7 @@
         <v>12</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>19</v>
@@ -2079,10 +2084,10 @@
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>19</v>
@@ -2099,13 +2104,13 @@
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -2119,13 +2124,13 @@
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -2142,7 +2147,7 @@
         <v>15</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>19</v>
@@ -2162,10 +2167,10 @@
         <v>15</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -2182,10 +2187,10 @@
         <v>15</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -2202,10 +2207,10 @@
         <v>15</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -2222,7 +2227,7 @@
         <v>15</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>9</v>
+        <v>83</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>6</v>
@@ -2230,10 +2235,10 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
@@ -2242,18 +2247,18 @@
         <v>15</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
@@ -2262,47 +2267,47 @@
         <v>15</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>15</v>
+        <v>89</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>15</v>
+        <v>83</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>89</v>
+        <v>4</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>6</v>
@@ -2310,19 +2315,19 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>6</v>
@@ -2330,19 +2335,19 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>6</v>
@@ -2350,19 +2355,19 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>6</v>
@@ -2370,19 +2375,19 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>6</v>
@@ -2390,19 +2395,19 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>6</v>
@@ -2410,19 +2415,19 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>6</v>
@@ -2430,19 +2435,19 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>6</v>
@@ -2450,19 +2455,19 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>6</v>
@@ -2470,19 +2475,19 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>111</v>
+        <v>86</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>6</v>
@@ -2499,10 +2504,10 @@
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>6</v>
@@ -2519,10 +2524,10 @@
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>6</v>
@@ -2539,10 +2544,10 @@
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>6</v>
@@ -2559,10 +2564,10 @@
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>6</v>
@@ -2959,73 +2964,73 @@
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B75" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B75" s="1" t="s">
-        <v>166</v>
-      </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>167</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D76" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B76" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="E76" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B77" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="C77" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F77" s="1" t="s">
         <v>171</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="E77" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F77" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -3039,13 +3044,13 @@
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>167</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -3059,10 +3064,10 @@
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>6</v>
@@ -3079,73 +3084,73 @@
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>179</v>
+        <v>19</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>179</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D83" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="B83" s="1" t="s">
+      <c r="E83" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F83" s="1" t="s">
         <v>185</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F83" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -3159,13 +3164,13 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>19</v>
+        <v>185</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -3179,90 +3184,90 @@
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="B86" s="1" t="s">
-        <v>192</v>
-      </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F88" s="1" t="s">
         <v>196</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F88" s="1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B89" s="1" t="s">
+      <c r="C89" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D89" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="C89" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>193</v>
-      </c>
       <c r="E89" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>19</v>
@@ -3279,13 +3284,13 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -3299,10 +3304,10 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>19</v>
@@ -3310,19 +3315,19 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="B92" s="1" t="s">
-        <v>206</v>
-      </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>19</v>
@@ -3330,39 +3335,39 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B93" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B94" s="1" t="s">
-        <v>210</v>
-      </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>19</v>
@@ -3370,22 +3375,22 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="B95" s="1" t="s">
+      <c r="C95" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D95" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="C95" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>204</v>
-      </c>
       <c r="E95" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -3399,13 +3404,13 @@
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3419,10 +3424,10 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>19</v>
@@ -3439,10 +3444,10 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>19</v>
@@ -3450,39 +3455,39 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B99" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="B99" s="1" t="s">
-        <v>221</v>
-      </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B100" s="1" t="s">
-        <v>223</v>
-      </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>19</v>
@@ -3490,19 +3495,19 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="B101" s="1" t="s">
+      <c r="C101" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D101" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="C101" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>219</v>
-      </c>
       <c r="E101" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>19</v>
@@ -3519,10 +3524,10 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>19</v>
@@ -3539,10 +3544,10 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>19</v>
@@ -3550,19 +3555,19 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="B104" s="1" t="s">
-        <v>232</v>
-      </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>19</v>
@@ -3570,42 +3575,42 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>234</v>
-      </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="B106" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="B106" s="1" t="s">
+      <c r="C106" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D106" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="C106" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>230</v>
-      </c>
       <c r="E106" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -3619,10 +3624,10 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>19</v>
@@ -3639,13 +3644,13 @@
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -3659,30 +3664,30 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="B110" s="1" t="s">
-        <v>245</v>
-      </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>19</v>
@@ -3690,19 +3695,19 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="B111" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>19</v>
@@ -3710,19 +3715,19 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="B112" s="1" t="s">
+      <c r="C112" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D112" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="C112" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>243</v>
-      </c>
       <c r="E112" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>19</v>
@@ -3739,10 +3744,10 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>19</v>
@@ -3759,10 +3764,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>19</v>
@@ -3779,10 +3784,10 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>89</v>
+        <v>9</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>19</v>
@@ -3799,10 +3804,10 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>19</v>
@@ -3810,19 +3815,19 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="B117" s="1" t="s">
+      <c r="C117" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D117" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="C117" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>258</v>
-      </c>
       <c r="E117" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>19</v>
@@ -3839,10 +3844,10 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>19</v>
@@ -3859,10 +3864,10 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>19</v>
@@ -3879,13 +3884,13 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -3899,10 +3904,10 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>6</v>
@@ -3910,22 +3915,22 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B122" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="B122" s="1" t="s">
+      <c r="C122" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D122" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="C122" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>269</v>
-      </c>
       <c r="E122" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>167</v>
+        <v>6</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -3939,13 +3944,13 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -3959,13 +3964,13 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>6</v>
+        <v>171</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -3979,13 +3984,13 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -3999,10 +4004,10 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>19</v>
@@ -4010,19 +4015,19 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B127" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="B127" s="1" t="s">
+      <c r="C127" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D127" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="C127" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>280</v>
-      </c>
       <c r="E127" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>19</v>
@@ -4039,10 +4044,10 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>19</v>
@@ -4059,10 +4064,10 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>19</v>
@@ -4079,10 +4084,10 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>19</v>
@@ -4099,10 +4104,10 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>19</v>
@@ -4119,13 +4124,13 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>167</v>
+        <v>19</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -4139,13 +4144,13 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -4159,13 +4164,13 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -4179,30 +4184,30 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>4</v>
+        <v>86</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>19</v>
+        <v>171</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="B136" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="B136" s="1" t="s">
+      <c r="C136" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D136" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="C136" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>299</v>
-      </c>
       <c r="E136" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>19</v>
@@ -4219,10 +4224,10 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>19</v>
@@ -4239,10 +4244,10 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>19</v>
@@ -4259,30 +4264,30 @@
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B140" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="B140" s="1" t="s">
+      <c r="C140" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D140" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="C140" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>308</v>
-      </c>
       <c r="E140" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>6</v>
@@ -4299,10 +4304,10 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>6</v>
@@ -4319,10 +4324,10 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>6</v>
@@ -4339,10 +4344,10 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>6</v>
@@ -4359,10 +4364,10 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>6</v>
@@ -4379,10 +4384,10 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>6</v>
@@ -4399,10 +4404,10 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>4</v>
+        <v>83</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>6</v>
@@ -4410,19 +4415,19 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B147" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="B147" s="1" t="s">
+      <c r="C147" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D147" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="C147" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>323</v>
-      </c>
       <c r="E147" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>6</v>
@@ -4439,10 +4444,10 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>6</v>
@@ -4459,10 +4464,10 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>6</v>
@@ -4479,10 +4484,10 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>6</v>
@@ -4499,10 +4504,10 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>6</v>
@@ -4510,19 +4515,19 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B152" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="B152" s="1" t="s">
+      <c r="C152" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D152" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="C152" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D152" s="1" t="s">
-        <v>334</v>
-      </c>
       <c r="E152" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>6</v>
@@ -4539,10 +4544,10 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>6</v>
@@ -4559,10 +4564,10 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>6</v>
@@ -4579,10 +4584,10 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>6</v>
@@ -4599,10 +4604,10 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>6</v>
@@ -4619,33 +4624,33 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>347</v>
+        <v>336</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="B158" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="B158" s="1" t="s">
+      <c r="C158" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D158" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="C158" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D158" s="1" t="s">
-        <v>347</v>
-      </c>
       <c r="E158" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>179</v>
+        <v>19</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -4659,13 +4664,13 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -4679,13 +4684,13 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -4699,13 +4704,13 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>19</v>
+        <v>185</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -4719,12 +4724,32 @@
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E162" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F162" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A163" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D163" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="E163" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F162" s="1" t="s">
+      <c r="F163" s="1" t="s">
         <v>19</v>
       </c>
     </row>

--- a/IFD04D.xlsx
+++ b/IFD04D.xlsx
@@ -856,7 +856,7 @@
     <t>20045610</t>
   </si>
   <si>
-    <t>SEDAAP MIE STO CUP81</t>
+    <t>SEDAP STO CUP 81 G</t>
   </si>
   <si>
     <t>24</t>
@@ -865,7 +865,7 @@
     <t>20052391</t>
   </si>
   <si>
-    <t>SEDAAP MIE K/S CUP81</t>
+    <t>SEDAP KR SPS C 81 G</t>
   </si>
   <si>
     <t>20130519</t>
@@ -877,19 +877,19 @@
     <t>20113844</t>
   </si>
   <si>
-    <t>SEDAAP MI AYM JRT 75</t>
+    <t>SEDAP AY-JR C 75 G</t>
   </si>
   <si>
     <t>20122255</t>
   </si>
   <si>
-    <t>SDP MI BASO BLDK 77G</t>
+    <t>SEDAP BSO-M C 77 G</t>
   </si>
   <si>
     <t>20135720</t>
   </si>
   <si>
-    <t>SDP MI KARI MRCON79G</t>
+    <t>SEDAP KR-MR C 79 G</t>
   </si>
   <si>
     <t>20098947</t>
@@ -928,13 +928,13 @@
     <t>20045609</t>
   </si>
   <si>
-    <t>SEDAAP MIE BSO CUP77</t>
+    <t>SEDAP BSO CUP 77 G</t>
   </si>
   <si>
     <t>20140678</t>
   </si>
   <si>
-    <t>SEDAAP SPC LAKSA CUP</t>
+    <t>SEDAP SPC-LKS C 86 G</t>
   </si>
   <si>
     <t>20016246</t>
